--- a/output/Tables/7000 steps/HIA_sex_Rubin_7000steps_1000replicate.xlsx
+++ b/output/Tables/7000 steps/HIA_sex_Rubin_7000steps_1000replicate.xlsx
@@ -438,22 +438,22 @@
         </is>
       </c>
       <c r="C2">
-        <v>60700.66</v>
+        <v>66175.189</v>
       </c>
       <c r="D2">
-        <v>57767.243</v>
+        <v>63007.026</v>
       </c>
       <c r="E2">
-        <v>63634.077</v>
+        <v>69343.351</v>
       </c>
       <c r="F2">
-        <v>708895.125</v>
+        <v>710852.613</v>
       </c>
       <c r="G2">
-        <v>691188.838</v>
+        <v>693453.683</v>
       </c>
       <c r="H2">
-        <v>726601.412</v>
+        <v>728251.542</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>94283051600.62399</v>
+        <v>94543397501.534</v>
       </c>
       <c r="M2">
-        <v>91928115421.543</v>
+        <v>92229339860.308</v>
       </c>
       <c r="N2">
-        <v>96637987779.705</v>
+        <v>96857455142.75999</v>
       </c>
     </row>
     <row r="3">
@@ -486,22 +486,22 @@
         </is>
       </c>
       <c r="C3">
-        <v>98308.13400000001</v>
+        <v>100994.243</v>
       </c>
       <c r="D3">
-        <v>93549.179</v>
+        <v>96121.981</v>
       </c>
       <c r="E3">
-        <v>103067.089</v>
+        <v>105866.504</v>
       </c>
       <c r="F3">
-        <v>943432.999</v>
+        <v>927457.286</v>
       </c>
       <c r="G3">
-        <v>915232.6459999999</v>
+        <v>900009.472</v>
       </c>
       <c r="H3">
-        <v>971633.352</v>
+        <v>954905.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>125476588826.749</v>
+        <v>123351819009.051</v>
       </c>
       <c r="M3">
-        <v>121725941883.805</v>
+        <v>119701259730.66</v>
       </c>
       <c r="N3">
-        <v>129227235769.692</v>
+        <v>127002378287.442</v>
       </c>
     </row>
     <row r="4">
@@ -534,40 +534,40 @@
         </is>
       </c>
       <c r="C4">
-        <v>62631.663</v>
+        <v>58459.464</v>
       </c>
       <c r="D4">
-        <v>60425.523</v>
+        <v>56426.75</v>
       </c>
       <c r="E4">
-        <v>64837.802</v>
+        <v>60492.178</v>
       </c>
       <c r="F4">
-        <v>63153.013</v>
+        <v>83659.399</v>
       </c>
       <c r="G4">
-        <v>61244.809</v>
+        <v>81132.762</v>
       </c>
       <c r="H4">
-        <v>65061.218</v>
+        <v>86186.037</v>
       </c>
       <c r="I4">
-        <v>3488708864.819</v>
+        <v>3080521452.37</v>
       </c>
       <c r="J4">
-        <v>3365822458.198</v>
+        <v>2973407593.133</v>
       </c>
       <c r="K4">
-        <v>3611595271.44</v>
+        <v>3187635311.607</v>
       </c>
       <c r="L4">
-        <v>8399350787.409</v>
+        <v>11126700094.898</v>
       </c>
       <c r="M4">
-        <v>8145559607.679</v>
+        <v>10790657325.438</v>
       </c>
       <c r="N4">
-        <v>8653141967.139999</v>
+        <v>11462742864.357</v>
       </c>
     </row>
     <row r="5">
@@ -582,40 +582,40 @@
         </is>
       </c>
       <c r="C5">
-        <v>83187.552</v>
+        <v>75149.988</v>
       </c>
       <c r="D5">
-        <v>80015.319</v>
+        <v>72281.68799999999</v>
       </c>
       <c r="E5">
-        <v>86359.78599999999</v>
+        <v>78018.288</v>
       </c>
       <c r="F5">
-        <v>67496.372</v>
+        <v>98164.232</v>
       </c>
       <c r="G5">
-        <v>65102.978</v>
+        <v>94672.10000000001</v>
       </c>
       <c r="H5">
-        <v>69889.76700000001</v>
+        <v>101656.364</v>
       </c>
       <c r="I5">
-        <v>4633713027.164</v>
+        <v>3960028613.811</v>
       </c>
       <c r="J5">
-        <v>4457013280.209</v>
+        <v>3808883524.725</v>
       </c>
       <c r="K5">
-        <v>4810412774.119</v>
+        <v>4111173702.896</v>
       </c>
       <c r="L5">
-        <v>8977017519.846001</v>
+        <v>13055842835.799</v>
       </c>
       <c r="M5">
-        <v>8658696040.933001</v>
+        <v>12591389246.354</v>
       </c>
       <c r="N5">
-        <v>9295338998.759001</v>
+        <v>13520296425.245</v>
       </c>
     </row>
     <row r="6">
@@ -630,40 +630,40 @@
         </is>
       </c>
       <c r="C6">
-        <v>79476.02099999999</v>
+        <v>12884.113</v>
       </c>
       <c r="D6">
-        <v>76911.10400000001</v>
+        <v>12494.021</v>
       </c>
       <c r="E6">
-        <v>82040.939</v>
+        <v>13274.206</v>
       </c>
       <c r="F6">
-        <v>141800.792</v>
+        <v>6793.511</v>
       </c>
       <c r="G6">
-        <v>136024.068</v>
+        <v>6593.94</v>
       </c>
       <c r="H6">
-        <v>147577.515</v>
+        <v>6993.081</v>
       </c>
       <c r="I6">
-        <v>1176801447.557</v>
+        <v>377749320.876</v>
       </c>
       <c r="J6">
-        <v>1138822717.246</v>
+        <v>366312192.562</v>
       </c>
       <c r="K6">
-        <v>1214780177.868</v>
+        <v>389186449.19</v>
       </c>
       <c r="L6">
-        <v>18859505291.088</v>
+        <v>903536917.926</v>
       </c>
       <c r="M6">
-        <v>18091201055.239</v>
+        <v>876994020.941</v>
       </c>
       <c r="N6">
-        <v>19627809526.937</v>
+        <v>930079814.911</v>
       </c>
     </row>
     <row r="7">
@@ -678,40 +678,40 @@
         </is>
       </c>
       <c r="C7">
-        <v>50181.992</v>
+        <v>16909.134</v>
       </c>
       <c r="D7">
-        <v>48187.399</v>
+        <v>16233.262</v>
       </c>
       <c r="E7">
-        <v>52176.584</v>
+        <v>17585.006</v>
       </c>
       <c r="F7">
-        <v>51287.364</v>
+        <v>7063.825</v>
       </c>
       <c r="G7">
-        <v>49186.967</v>
+        <v>6789.628</v>
       </c>
       <c r="H7">
-        <v>53387.761</v>
+        <v>7338.023</v>
       </c>
       <c r="I7">
-        <v>743044751.154</v>
+        <v>495758889.041</v>
       </c>
       <c r="J7">
-        <v>713510823.881</v>
+        <v>475942995.117</v>
       </c>
       <c r="K7">
-        <v>772578678.428</v>
+        <v>515574782.965</v>
       </c>
       <c r="L7">
-        <v>6821219412.73</v>
+        <v>939488764.5599999</v>
       </c>
       <c r="M7">
-        <v>6541866564.903</v>
+        <v>903020473.794</v>
       </c>
       <c r="N7">
-        <v>7100572260.557</v>
+        <v>975957055.327</v>
       </c>
     </row>
     <row r="8">
@@ -726,40 +726,40 @@
         </is>
       </c>
       <c r="C8">
-        <v>11899.675</v>
+        <v>8833.112999999999</v>
       </c>
       <c r="D8">
-        <v>11468.14</v>
+        <v>8574.558999999999</v>
       </c>
       <c r="E8">
-        <v>12331.209</v>
+        <v>9091.665999999999</v>
       </c>
       <c r="F8">
-        <v>25211.315</v>
+        <v>15700.806</v>
       </c>
       <c r="G8">
-        <v>24296.434</v>
+        <v>15242.364</v>
       </c>
       <c r="H8">
-        <v>26126.196</v>
+        <v>16159.247</v>
       </c>
       <c r="I8">
-        <v>894867430.852</v>
+        <v>346266856.029</v>
       </c>
       <c r="J8">
-        <v>862415580.3150001</v>
+        <v>336131300.406</v>
       </c>
       <c r="K8">
-        <v>927319281.3890001</v>
+        <v>356402411.653</v>
       </c>
       <c r="L8">
-        <v>3353104893.601</v>
+        <v>2088207154.34</v>
       </c>
       <c r="M8">
-        <v>3231425730.692</v>
+        <v>2027234431.793</v>
       </c>
       <c r="N8">
-        <v>3474784056.51</v>
+        <v>2149179876.888</v>
       </c>
     </row>
     <row r="9">
@@ -774,40 +774,40 @@
         </is>
       </c>
       <c r="C9">
-        <v>15821.703</v>
+        <v>11626.777</v>
       </c>
       <c r="D9">
-        <v>15245.81</v>
+        <v>11243.163</v>
       </c>
       <c r="E9">
-        <v>16397.595</v>
+        <v>12010.392</v>
       </c>
       <c r="F9">
-        <v>29365.176</v>
+        <v>21869.472</v>
       </c>
       <c r="G9">
-        <v>28167.218</v>
+        <v>21115.769</v>
       </c>
       <c r="H9">
-        <v>30563.135</v>
+        <v>22623.176</v>
       </c>
       <c r="I9">
-        <v>1189807851.255</v>
+        <v>455781300.176</v>
       </c>
       <c r="J9">
-        <v>1146500131.085</v>
+        <v>440743213.892</v>
       </c>
       <c r="K9">
-        <v>1233115571.424</v>
+        <v>470819386.46</v>
       </c>
       <c r="L9">
-        <v>3905568468.424</v>
+        <v>2908639828.389</v>
       </c>
       <c r="M9">
-        <v>3746240011.697</v>
+        <v>2808397248.644</v>
       </c>
       <c r="N9">
-        <v>4064896925.151</v>
+        <v>3008882408.134</v>
       </c>
     </row>
     <row r="10">
@@ -822,40 +822,40 @@
         </is>
       </c>
       <c r="C10">
-        <v>29326.988</v>
+        <v>28231.794</v>
       </c>
       <c r="D10">
-        <v>27793.103</v>
+        <v>26835.058</v>
       </c>
       <c r="E10">
-        <v>30860.874</v>
+        <v>29628.531</v>
       </c>
       <c r="F10">
-        <v>56524.536</v>
+        <v>32307.063</v>
       </c>
       <c r="G10">
-        <v>54391.819</v>
+        <v>30673.307</v>
       </c>
       <c r="H10">
-        <v>58657.253</v>
+        <v>33940.819</v>
       </c>
       <c r="I10">
-        <v>493837156</v>
+        <v>470002914.196</v>
       </c>
       <c r="J10">
-        <v>468008061.473</v>
+        <v>446750044.345</v>
       </c>
       <c r="K10">
-        <v>519666250.527</v>
+        <v>493255784.047</v>
       </c>
       <c r="L10">
-        <v>7517763297.851</v>
+        <v>4296839335.31</v>
       </c>
       <c r="M10">
-        <v>7234111987.651</v>
+        <v>4079549793.396</v>
       </c>
       <c r="N10">
-        <v>7801414608.051</v>
+        <v>4514128877.224</v>
       </c>
     </row>
     <row r="11">
@@ -870,40 +870,40 @@
         </is>
       </c>
       <c r="C11">
-        <v>21855.794</v>
+        <v>20030.614</v>
       </c>
       <c r="D11">
-        <v>20507.687</v>
+        <v>18827.468</v>
       </c>
       <c r="E11">
-        <v>23203.901</v>
+        <v>21233.76</v>
       </c>
       <c r="F11">
-        <v>25214.54</v>
+        <v>22918.229</v>
       </c>
       <c r="G11">
-        <v>24089.624</v>
+        <v>21509.452</v>
       </c>
       <c r="H11">
-        <v>26339.457</v>
+        <v>24327.007</v>
       </c>
       <c r="I11">
-        <v>368029717.341</v>
+        <v>333469661.779</v>
       </c>
       <c r="J11">
-        <v>345328948.73</v>
+        <v>313439686.519</v>
       </c>
       <c r="K11">
-        <v>390730485.953</v>
+        <v>353499637.039</v>
       </c>
       <c r="L11">
-        <v>3353533875.92</v>
+        <v>3048124519.47</v>
       </c>
       <c r="M11">
-        <v>3203919941.151</v>
+        <v>2860757121.431</v>
       </c>
       <c r="N11">
-        <v>3503147810.688</v>
+        <v>3235491917.508</v>
       </c>
     </row>
     <row r="12">
@@ -918,22 +918,22 @@
         </is>
       </c>
       <c r="C12">
-        <v>412624.71</v>
+        <v>294866.038</v>
       </c>
       <c r="D12">
-        <v>402688.831</v>
+        <v>287949.52</v>
       </c>
       <c r="E12">
-        <v>422560.589</v>
+        <v>301782.557</v>
       </c>
       <c r="F12">
-        <v>1258787.101</v>
+        <v>113040.428</v>
       </c>
       <c r="G12">
-        <v>1214461.044</v>
+        <v>109404.87</v>
       </c>
       <c r="H12">
-        <v>1303113.157</v>
+        <v>116675.985</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -945,13 +945,13 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>167418684377.693</v>
+        <v>15034376878.642</v>
       </c>
       <c r="M12">
-        <v>161523318810.014</v>
+        <v>14550847722.778</v>
       </c>
       <c r="N12">
-        <v>173314049945.371</v>
+        <v>15517906034.507</v>
       </c>
     </row>
     <row r="13">
@@ -966,22 +966,22 @@
         </is>
       </c>
       <c r="C13">
-        <v>204591.813</v>
+        <v>145007.11</v>
       </c>
       <c r="D13">
-        <v>198850.493</v>
+        <v>141062.762</v>
       </c>
       <c r="E13">
-        <v>210333.132</v>
+        <v>148951.459</v>
       </c>
       <c r="F13">
-        <v>529481.102</v>
+        <v>47607.562</v>
       </c>
       <c r="G13">
-        <v>508594.203</v>
+        <v>45821.448</v>
       </c>
       <c r="H13">
-        <v>550368.001</v>
+        <v>49393.676</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -993,13 +993,13 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>70420986565.56599</v>
+        <v>6331805765.92</v>
       </c>
       <c r="M13">
-        <v>67643028947.368</v>
+        <v>6094252603.915</v>
       </c>
       <c r="N13">
-        <v>73198944183.76401</v>
+        <v>6569358927.925</v>
       </c>
     </row>
   </sheetData>
